--- a/assets/Матрица_компетенций_WEB.xlsx
+++ b/assets/Матрица_компетенций_WEB.xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\fsk\vdi\Folders\ukolovaaa\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\probl\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85A29ADC-72A4-4CA2-9A21-0977761E2ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1780ABD8-7277-4504-894A-34C756E6C404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Перечень компетенций" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Перечень компетенций'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Перечень компетенций'!$A$1:$I$47</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="96">
   <si>
     <t>Тип компетенции (Hard/Soft)</t>
   </si>
@@ -351,12 +351,28 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -505,109 +521,124 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -893,21 +924,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBBB767E-C84C-4CE4-8559-2D5C098FF150}">
   <dimension ref="A1:I49"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="24.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="40.44140625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="58.5546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" style="4" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="11.33203125" style="4" customWidth="1"/>
-    <col min="10" max="16384" width="8.6640625" style="1"/>
+    <col min="1" max="1" width="17.6328125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24.36328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="40.453125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="58.54296875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11.6328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.54296875" style="4" customWidth="1"/>
+    <col min="7" max="7" width="12.36328125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="11.453125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="11.36328125" style="4" customWidth="1"/>
+    <col min="10" max="16384" width="8.6328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -936,36 +967,36 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="22" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="39" t="s">
+      <c r="C2" s="38" t="s">
         <v>11</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>12</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F2" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="24">
-        <v>2</v>
-      </c>
-      <c r="H2" s="24">
-        <v>3</v>
-      </c>
-      <c r="I2" s="24">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G2" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="I2" s="40" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="22" t="s">
         <v>9</v>
       </c>
@@ -984,17 +1015,17 @@
       <c r="F3" s="25">
         <v>1</v>
       </c>
-      <c r="G3" s="25">
-        <v>2</v>
-      </c>
-      <c r="H3" s="25">
-        <v>2</v>
-      </c>
-      <c r="I3" s="25">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G3" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="22" t="s">
         <v>9</v>
       </c>
@@ -1004,7 +1035,7 @@
       <c r="C4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="44" t="s">
         <v>17</v>
       </c>
       <c r="E4" s="24">
@@ -1013,24 +1044,24 @@
       <c r="F4" s="25">
         <v>1</v>
       </c>
-      <c r="G4" s="25">
-        <v>2</v>
-      </c>
-      <c r="H4" s="25">
-        <v>2</v>
-      </c>
-      <c r="I4" s="25">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G4" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="39" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="22" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="39" t="s">
+      <c r="C5" s="38" t="s">
         <v>95</v>
       </c>
       <c r="D5" s="9" t="s">
@@ -1042,17 +1073,17 @@
       <c r="F5" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="25">
-        <v>2</v>
-      </c>
-      <c r="H5" s="25">
-        <v>3</v>
-      </c>
-      <c r="I5" s="25">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G5" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" s="39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="22" t="s">
         <v>9</v>
       </c>
@@ -1071,17 +1102,17 @@
       <c r="F6" s="25">
         <v>1</v>
       </c>
-      <c r="G6" s="25">
-        <v>2</v>
-      </c>
-      <c r="H6" s="25">
-        <v>2</v>
-      </c>
-      <c r="I6" s="25">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G6" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" s="39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" s="22" t="s">
         <v>9</v>
       </c>
@@ -1091,33 +1122,33 @@
       <c r="C7" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="44" t="s">
         <v>91</v>
       </c>
       <c r="E7" s="24">
         <v>1</v>
       </c>
-      <c r="F7" s="25">
-        <v>2</v>
-      </c>
-      <c r="G7" s="25">
-        <v>3</v>
-      </c>
-      <c r="H7" s="25">
-        <v>3</v>
-      </c>
-      <c r="I7" s="25">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="F7" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="43" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" s="22" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="39" t="s">
+      <c r="C8" s="38" t="s">
         <v>93</v>
       </c>
       <c r="D8" s="18" t="s">
@@ -1126,27 +1157,27 @@
       <c r="E8" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="H8" s="25">
-        <v>3</v>
-      </c>
-      <c r="I8" s="25">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F8" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="I8" s="39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="22" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="C9" s="38" t="s">
         <v>94</v>
       </c>
       <c r="D9" s="18" t="s">
@@ -1158,17 +1189,17 @@
       <c r="F9" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="H9" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="26" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G9" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="I9" s="39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="22" t="s">
         <v>9</v>
       </c>
@@ -1187,17 +1218,17 @@
       <c r="F10" s="25">
         <v>0</v>
       </c>
-      <c r="G10" s="25">
-        <v>2</v>
-      </c>
-      <c r="H10" s="25">
-        <v>2</v>
-      </c>
-      <c r="I10" s="25">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G10" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="22" t="s">
         <v>9</v>
       </c>
@@ -1216,17 +1247,17 @@
       <c r="F11" s="25">
         <v>0</v>
       </c>
-      <c r="G11" s="25">
-        <v>2</v>
-      </c>
-      <c r="H11" s="25">
-        <v>2</v>
-      </c>
-      <c r="I11" s="25">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G11" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="22" t="s">
         <v>28</v>
       </c>
@@ -1239,14 +1270,14 @@
       <c r="D12" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="24">
-        <v>2</v>
-      </c>
-      <c r="F12" s="24">
-        <v>2</v>
-      </c>
-      <c r="G12" s="24">
-        <v>2</v>
+      <c r="E12" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="40" t="s">
+        <v>36</v>
       </c>
       <c r="H12" s="23" t="s">
         <v>31</v>
@@ -1255,7 +1286,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="58" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="22" t="s">
         <v>9</v>
       </c>
@@ -1265,17 +1296,17 @@
       <c r="C13" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="E13" s="24">
-        <v>2</v>
-      </c>
-      <c r="F13" s="24">
-        <v>2</v>
-      </c>
-      <c r="G13" s="24">
-        <v>2</v>
+      <c r="E13" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="40" t="s">
+        <v>36</v>
       </c>
       <c r="H13" s="23" t="s">
         <v>31</v>
@@ -1284,14 +1315,14 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="22" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="38" t="s">
         <v>18</v>
       </c>
       <c r="D14" s="9" t="s">
@@ -1303,17 +1334,17 @@
       <c r="F14" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="H14" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="25" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G14" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="I14" s="39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="22" t="s">
         <v>9</v>
       </c>
@@ -1332,17 +1363,17 @@
       <c r="F15" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G15" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="H15" s="25">
-        <v>2</v>
-      </c>
-      <c r="I15" s="25">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="G15" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="I15" s="39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A16" s="22" t="s">
         <v>9</v>
       </c>
@@ -1361,17 +1392,17 @@
       <c r="F16" s="25">
         <v>0</v>
       </c>
-      <c r="G16" s="25">
-        <v>1</v>
-      </c>
-      <c r="H16" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="I16" s="25" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G16" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" s="39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="22" t="s">
         <v>9</v>
       </c>
@@ -1384,23 +1415,23 @@
       <c r="D17" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E17" s="24">
-        <v>2</v>
+      <c r="E17" s="40" t="s">
+        <v>13</v>
       </c>
       <c r="F17" s="25">
         <v>2</v>
       </c>
-      <c r="G17" s="25">
-        <v>3</v>
-      </c>
-      <c r="H17" s="25">
-        <v>3</v>
-      </c>
-      <c r="I17" s="25">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="G17" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="H17" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="I17" s="43" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A18" s="22" t="s">
         <v>9</v>
       </c>
@@ -1411,23 +1442,23 @@
         <v>45</v>
       </c>
       <c r="D18" s="9"/>
-      <c r="E18" s="24">
-        <v>2</v>
-      </c>
-      <c r="F18" s="24">
-        <v>2</v>
-      </c>
-      <c r="G18" s="25">
-        <v>3</v>
-      </c>
-      <c r="H18" s="25">
-        <v>3</v>
-      </c>
-      <c r="I18" s="25">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="E18" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="H18" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="I18" s="39" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A19" s="22" t="s">
         <v>9</v>
       </c>
@@ -1441,20 +1472,20 @@
       <c r="E19" s="24">
         <v>0</v>
       </c>
-      <c r="F19" s="25">
-        <v>0</v>
-      </c>
-      <c r="G19" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="H19" s="25">
-        <v>2</v>
-      </c>
-      <c r="I19" s="25" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F19" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="I19" s="39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="22" t="s">
         <v>9</v>
       </c>
@@ -1471,17 +1502,17 @@
       <c r="F20" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G20" s="25">
-        <v>3</v>
-      </c>
-      <c r="H20" s="25">
-        <v>3</v>
-      </c>
-      <c r="I20" s="25">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G20" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="H20" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="I20" s="39" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="22" t="s">
         <v>9</v>
       </c>
@@ -1498,17 +1529,17 @@
       <c r="F21" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G21" s="25">
-        <v>3</v>
-      </c>
-      <c r="H21" s="25">
-        <v>3</v>
-      </c>
-      <c r="I21" s="25">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G21" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="22" t="s">
         <v>9</v>
       </c>
@@ -1525,17 +1556,17 @@
       <c r="F22" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G22" s="25">
-        <v>3</v>
-      </c>
-      <c r="H22" s="25">
-        <v>3</v>
-      </c>
-      <c r="I22" s="25">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G22" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="I22" s="39" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="22" t="s">
         <v>9</v>
       </c>
@@ -1552,24 +1583,24 @@
       <c r="F23" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G23" s="25">
-        <v>3</v>
-      </c>
-      <c r="H23" s="25">
-        <v>3</v>
-      </c>
-      <c r="I23" s="25">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G23" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="H23" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="I23" s="39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="22" t="s">
         <v>28</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="39" t="s">
+      <c r="C24" s="38" t="s">
         <v>52</v>
       </c>
       <c r="D24" s="9" t="s">
@@ -1581,17 +1612,17 @@
       <c r="F24" s="25">
         <v>0</v>
       </c>
-      <c r="G24" s="25">
-        <v>1</v>
-      </c>
-      <c r="H24" s="25">
-        <v>1</v>
-      </c>
-      <c r="I24" s="25" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G24" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="I24" s="39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="22" t="s">
         <v>9</v>
       </c>
@@ -1608,17 +1639,17 @@
       <c r="F25" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="G25" s="24">
-        <v>2</v>
-      </c>
-      <c r="H25" s="24">
-        <v>3</v>
-      </c>
-      <c r="I25" s="24">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="G25" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="I25" s="40" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A26" s="22" t="s">
         <v>9</v>
       </c>
@@ -1635,17 +1666,17 @@
       <c r="F26" s="24">
         <v>2</v>
       </c>
-      <c r="G26" s="24">
-        <v>2</v>
-      </c>
-      <c r="H26" s="24">
-        <v>2</v>
-      </c>
-      <c r="I26" s="24">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G26" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="H26" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="I26" s="40" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="22" t="s">
         <v>9</v>
       </c>
@@ -1662,17 +1693,17 @@
       <c r="F27" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="G27" s="24">
-        <v>2</v>
-      </c>
-      <c r="H27" s="24">
-        <v>2</v>
-      </c>
-      <c r="I27" s="24" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G27" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="I27" s="40" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="22" t="s">
         <v>9</v>
       </c>
@@ -1689,17 +1720,17 @@
       <c r="F28" s="24">
         <v>0</v>
       </c>
-      <c r="G28" s="24">
-        <v>1</v>
-      </c>
-      <c r="H28" s="24">
-        <v>2</v>
-      </c>
-      <c r="I28" s="24">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" s="21" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G28" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="I28" s="40" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" s="21" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A29" s="31" t="s">
         <v>9</v>
       </c>
@@ -1712,24 +1743,24 @@
       <c r="D29" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="E29" s="33">
-        <v>2</v>
-      </c>
-      <c r="F29" s="33">
-        <v>2</v>
-      </c>
-      <c r="G29" s="33">
-        <v>2</v>
-      </c>
-      <c r="H29" s="33">
-        <v>2</v>
-      </c>
-      <c r="I29" s="33">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="34" t="s">
+      <c r="E29" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="F29" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="G29" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="I29" s="41" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30" s="33" t="s">
         <v>9</v>
       </c>
       <c r="B30" s="12" t="s">
@@ -1745,18 +1776,18 @@
       <c r="F30" s="24">
         <v>0</v>
       </c>
-      <c r="G30" s="24">
-        <v>0</v>
-      </c>
-      <c r="H30" s="24">
-        <v>0</v>
-      </c>
-      <c r="I30" s="25">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="34" t="s">
+      <c r="G30" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="I30" s="39" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31" s="33" t="s">
         <v>9</v>
       </c>
       <c r="B31" s="12" t="s">
@@ -1772,18 +1803,18 @@
       <c r="F31" s="24">
         <v>2</v>
       </c>
-      <c r="G31" s="24">
-        <v>2</v>
-      </c>
-      <c r="H31" s="24">
-        <v>2</v>
-      </c>
-      <c r="I31" s="24">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="35" t="s">
+      <c r="G31" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="H31" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="I31" s="40" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A32" s="34" t="s">
         <v>9</v>
       </c>
       <c r="B32" s="12" t="s">
@@ -1799,18 +1830,18 @@
       <c r="F32" s="25">
         <v>0</v>
       </c>
-      <c r="G32" s="25">
-        <v>0</v>
-      </c>
-      <c r="H32" s="25">
-        <v>2</v>
-      </c>
-      <c r="I32" s="25">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="35" t="s">
+      <c r="G32" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="I32" s="39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A33" s="34" t="s">
         <v>28</v>
       </c>
       <c r="B33" s="12" t="s">
@@ -1826,18 +1857,18 @@
       <c r="F33" s="25">
         <v>0</v>
       </c>
-      <c r="G33" s="25">
-        <v>0</v>
-      </c>
-      <c r="H33" s="25">
-        <v>0</v>
-      </c>
-      <c r="I33" s="25">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="35" t="s">
+      <c r="G33" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="I33" s="43" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A34" s="34" t="s">
         <v>28</v>
       </c>
       <c r="B34" s="12" t="s">
@@ -1847,24 +1878,24 @@
         <v>66</v>
       </c>
       <c r="D34" s="13"/>
-      <c r="E34" s="25" t="s">
-        <v>13</v>
+      <c r="E34" s="39" t="s">
+        <v>20</v>
       </c>
       <c r="F34" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G34" s="25">
-        <v>2</v>
-      </c>
-      <c r="H34" s="25">
-        <v>2</v>
-      </c>
-      <c r="I34" s="25" t="s">
+      <c r="G34" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="I34" s="39" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="35" t="s">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A35" s="34" t="s">
         <v>28</v>
       </c>
       <c r="B35" s="12" t="s">
@@ -1880,18 +1911,18 @@
       <c r="F35" s="25">
         <v>2</v>
       </c>
-      <c r="G35" s="25">
-        <v>2</v>
-      </c>
-      <c r="H35" s="25">
-        <v>2</v>
-      </c>
-      <c r="I35" s="25">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="36" t="s">
+      <c r="G35" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="H35" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="I35" s="39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="A36" s="35" t="s">
         <v>28</v>
       </c>
       <c r="B36" s="11" t="s">
@@ -1903,24 +1934,24 @@
       <c r="D36" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E36" s="25">
-        <v>2</v>
-      </c>
-      <c r="F36" s="25">
-        <v>2</v>
-      </c>
-      <c r="G36" s="25">
-        <v>2</v>
-      </c>
-      <c r="H36" s="25">
-        <v>2</v>
-      </c>
-      <c r="I36" s="25">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A37" s="36" t="s">
+      <c r="E36" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H36" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="I36" s="39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="A37" s="35" t="s">
         <v>28</v>
       </c>
       <c r="B37" s="11" t="s">
@@ -1932,24 +1963,24 @@
       <c r="D37" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E37" s="25">
-        <v>2</v>
-      </c>
-      <c r="F37" s="25">
-        <v>2</v>
-      </c>
-      <c r="G37" s="25">
-        <v>2</v>
-      </c>
-      <c r="H37" s="25">
-        <v>2</v>
-      </c>
-      <c r="I37" s="25">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38" s="35" t="s">
+      <c r="E37" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="F37" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H37" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="I37" s="39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A38" s="34" t="s">
         <v>28</v>
       </c>
       <c r="B38" s="12" t="s">
@@ -1959,24 +1990,24 @@
         <v>72</v>
       </c>
       <c r="D38" s="13"/>
-      <c r="E38" s="25">
-        <v>2</v>
-      </c>
-      <c r="F38" s="25">
-        <v>2</v>
-      </c>
-      <c r="G38" s="25">
-        <v>2</v>
-      </c>
-      <c r="H38" s="25">
-        <v>2</v>
-      </c>
-      <c r="I38" s="25">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" s="35" t="s">
+      <c r="E38" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="H38" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="I38" s="39" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A39" s="34" t="s">
         <v>9</v>
       </c>
       <c r="B39" s="12" t="s">
@@ -1994,18 +2025,18 @@
       <c r="F39" s="25">
         <v>0</v>
       </c>
-      <c r="G39" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="H39" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="I39" s="25" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="35" t="s">
+      <c r="G39" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H39" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="I39" s="39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A40" s="34" t="s">
         <v>9</v>
       </c>
       <c r="B40" s="12" t="s">
@@ -2021,18 +2052,18 @@
       <c r="F40" s="25">
         <v>0</v>
       </c>
-      <c r="G40" s="25">
-        <v>1</v>
-      </c>
-      <c r="H40" s="25">
-        <v>1</v>
-      </c>
-      <c r="I40" s="25">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="35" t="s">
+      <c r="G40" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H40" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="I40" s="39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A41" s="34" t="s">
         <v>9</v>
       </c>
       <c r="B41" s="12" t="s">
@@ -2048,18 +2079,18 @@
       <c r="F41" s="25">
         <v>0</v>
       </c>
-      <c r="G41" s="25">
-        <v>1</v>
-      </c>
-      <c r="H41" s="25">
-        <v>1</v>
-      </c>
-      <c r="I41" s="25">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="35" t="s">
+      <c r="G41" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="H41" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="I41" s="39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A42" s="34" t="s">
         <v>9</v>
       </c>
       <c r="B42" s="12" t="s">
@@ -2072,27 +2103,27 @@
       <c r="E42" s="25">
         <v>0</v>
       </c>
-      <c r="F42" s="25">
-        <v>0</v>
-      </c>
-      <c r="G42" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="H42" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="I42" s="25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" s="35" t="s">
+      <c r="F42" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="G42" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="H42" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="I42" s="39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A43" s="34" t="s">
         <v>9</v>
       </c>
       <c r="B43" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="C43" s="37" t="s">
+      <c r="C43" s="36" t="s">
         <v>79</v>
       </c>
       <c r="D43" s="28" t="s">
@@ -2104,24 +2135,24 @@
       <c r="F43" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G43" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="H43" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="I43" s="25" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="35" t="s">
+      <c r="G43" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H43" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="I43" s="43" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A44" s="34" t="s">
         <v>9</v>
       </c>
       <c r="B44" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="C44" s="38" t="s">
+      <c r="C44" s="37" t="s">
         <v>84</v>
       </c>
       <c r="D44" s="28"/>
@@ -2131,24 +2162,24 @@
       <c r="F44" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="G44" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="H44" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="I44" s="26" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="35" t="s">
+      <c r="G44" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="I44" s="39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A45" s="34" t="s">
         <v>9</v>
       </c>
       <c r="B45" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="C45" s="38" t="s">
+      <c r="C45" s="37" t="s">
         <v>85</v>
       </c>
       <c r="D45" s="28"/>
@@ -2158,24 +2189,24 @@
       <c r="F45" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="G45" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="H45" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="I45" s="26" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="35" t="s">
+      <c r="G45" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H45" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="I45" s="39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A46" s="34" t="s">
         <v>9</v>
       </c>
       <c r="B46" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="C46" s="38" t="s">
+      <c r="C46" s="37" t="s">
         <v>87</v>
       </c>
       <c r="D46" s="28" t="s">
@@ -2184,21 +2215,21 @@
       <c r="E46" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="F46" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="G46" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="H46" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="I46" s="26" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="35" t="s">
+      <c r="F46" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="G46" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H46" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="I46" s="39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A47" s="34" t="s">
         <v>9</v>
       </c>
       <c r="B47" s="12" t="s">
@@ -2214,17 +2245,17 @@
       <c r="F47" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="G47" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="H47" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="I47" s="25" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G47" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="H47" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="I47" s="39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" s="14"/>
       <c r="B49" s="10"/>
       <c r="C49" s="15"/>
@@ -2236,7 +2267,7 @@
       <c r="I49" s="16"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1" xr:uid="{FBBB767E-C84C-4CE4-8559-2D5C098FF150}"/>
+  <autoFilter ref="A1:I47" xr:uid="{FBBB767E-C84C-4CE4-8559-2D5C098FF150}"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A1048576" xr:uid="{FFF2E545-3835-413A-B4B5-85DC260E9CEA}">
       <formula1>#REF!</formula1>
